--- a/src/test/fixtures/catalogs-http/imports/en/template.xlsx
+++ b/src/test/fixtures/catalogs-http/imports/en/template.xlsx
@@ -24,13 +24,13 @@
     <x:t>Text</x:t>
   </x:si>
   <x:si>
-    <x:t>English text</x:t>
+    <x:t>Spanish text</x:t>
   </x:si>
   <x:si>
     <x:t>Detail</x:t>
   </x:si>
   <x:si>
-    <x:t>English detail</x:t>
+    <x:t>Spanish detail</x:t>
   </x:si>
   <x:si>
     <x:t>Active</x:t>
